--- a/data/trans_orig/Viv_Temp_insuf-Habitat-trans_orig.xlsx
+++ b/data/trans_orig/Viv_Temp_insuf-Habitat-trans_orig.xlsx
@@ -541,7 +541,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -552,7 +552,7 @@
       <c r="I1" s="3" t="n"/>
       <c r="J1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="K1" s="3" t="n"/>
@@ -720,72 +720,72 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>55</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>39555</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>30138</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>50918</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>31,42%</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>23,94%</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>40,44%</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
           <t>63</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t>38869</t>
-        </is>
-      </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>31508</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>48490</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>33,14%</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>26,87%</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>41,35%</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>55</t>
-        </is>
-      </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>40522</t>
+          <t>41050</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>29882</t>
+          <t>32911</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>52144</t>
+          <t>50404</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>28,86%</t>
+          <t>33,91%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>21,28%</t>
+          <t>27,18%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>37,14%</t>
+          <t>41,63%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -795,32 +795,32 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>79392</t>
+          <t>80605</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>64704</t>
+          <t>64930</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>93462</t>
+          <t>93272</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>30,81%</t>
+          <t>32,64%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>25,11%</t>
+          <t>26,29%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>36,27%</t>
+          <t>37,77%</t>
         </is>
       </c>
     </row>
@@ -833,72 +833,72 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>116</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>86351</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>74988</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>95768</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>68,58%</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>59,56%</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>76,06%</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
           <t>133</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
-        <is>
-          <t>78411</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>68790</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>85772</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>66,86%</t>
-        </is>
-      </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>58,65%</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>73,13%</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>116</t>
-        </is>
-      </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>99890</t>
+          <t>80021</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>88268</t>
+          <t>70667</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>110530</t>
+          <t>88160</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>71,14%</t>
+          <t>66,09%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>62,86%</t>
+          <t>58,37%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>78,72%</t>
+          <t>72,82%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -908,32 +908,32 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>178301</t>
+          <t>166372</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>164231</t>
+          <t>153705</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>192989</t>
+          <t>182047</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>69,19%</t>
+          <t>67,36%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>63,73%</t>
+          <t>62,23%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>74,89%</t>
+          <t>73,71%</t>
         </is>
       </c>
     </row>
@@ -946,57 +946,57 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>171</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>125906</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>125906</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>125906</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
           <t>196</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
-        <is>
-          <t>117280</t>
-        </is>
-      </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>117280</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>117280</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>171</t>
-        </is>
-      </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>140412</t>
+          <t>121071</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>140412</t>
+          <t>121071</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>140412</t>
+          <t>121071</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1021,17 +1021,17 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>257693</t>
+          <t>246977</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>257693</t>
+          <t>246977</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>257693</t>
+          <t>246977</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1063,72 +1063,72 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>145</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>105771</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>92058</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>120830</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>44,59%</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>38,81%</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>50,94%</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
           <t>122</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
-        <is>
-          <t>82611</t>
-        </is>
-      </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>69889</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>94511</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
-        <is>
-          <t>43,59%</t>
-        </is>
-      </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>36,88%</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>49,87%</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>145</t>
-        </is>
-      </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>108680</t>
+          <t>83306</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>93978</t>
+          <t>72006</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>123247</t>
+          <t>95135</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>42,61%</t>
+          <t>45,44%</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>36,85%</t>
+          <t>39,28%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>48,33%</t>
+          <t>51,89%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1138,32 +1138,32 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>191291</t>
+          <t>189077</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>172144</t>
+          <t>170566</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>211654</t>
+          <t>207647</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
         <is>
-          <t>43,03%</t>
+          <t>44,96%</t>
         </is>
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>38,72%</t>
+          <t>40,56%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>47,61%</t>
+          <t>49,38%</t>
         </is>
       </c>
     </row>
@@ -1176,72 +1176,72 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>198</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>131435</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>116376</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>145148</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>55,41%</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>49,06%</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>61,19%</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
           <t>157</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
-        <is>
-          <t>106902</t>
-        </is>
-      </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>95002</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>119624</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>56,41%</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>50,13%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>63,12%</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>198</t>
-        </is>
-      </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>146355</t>
+          <t>100031</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>131788</t>
+          <t>88202</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>161057</t>
+          <t>111331</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>57,39%</t>
+          <t>54,56%</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>51,67%</t>
+          <t>48,11%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>63,15%</t>
+          <t>60,72%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1251,32 +1251,32 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>253257</t>
+          <t>231466</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>232894</t>
+          <t>212896</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>272404</t>
+          <t>249977</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
         <is>
-          <t>56,97%</t>
+          <t>55,04%</t>
         </is>
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>52,39%</t>
+          <t>50,62%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>61,28%</t>
+          <t>59,44%</t>
         </is>
       </c>
     </row>
@@ -1289,57 +1289,57 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
+          <t>343</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>237206</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>237206</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>237206</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
           <t>279</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
-        <is>
-          <t>189513</t>
-        </is>
-      </c>
-      <c r="E9" s="2" t="inlineStr">
-        <is>
-          <t>189513</t>
-        </is>
-      </c>
-      <c r="F9" s="2" t="inlineStr">
-        <is>
-          <t>189513</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>343</t>
-        </is>
-      </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>255035</t>
+          <t>183337</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>255035</t>
+          <t>183337</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>255035</t>
+          <t>183337</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1364,17 +1364,17 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>444548</t>
+          <t>420543</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>444548</t>
+          <t>420543</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>444548</t>
+          <t>420543</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -1406,72 +1406,72 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>65</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>48514</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>37770</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>60266</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>28,82%</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>22,44%</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>35,8%</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
           <t>73</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
-        <is>
-          <t>54035</t>
-        </is>
-      </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>32361</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>68743</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>28,38%</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>17,0%</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>36,1%</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>65</t>
-        </is>
-      </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>53588</t>
+          <t>50497</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>41430</t>
+          <t>40281</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>66453</t>
+          <t>60559</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>28,92%</t>
+          <t>32,15%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>22,36%</t>
+          <t>25,65%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>35,87%</t>
+          <t>38,56%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1481,32 +1481,32 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>107623</t>
+          <t>99011</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>81854</t>
+          <t>82186</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>128942</t>
+          <t>113483</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>28,65%</t>
+          <t>30,43%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>21,79%</t>
+          <t>25,26%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>34,32%</t>
+          <t>34,88%</t>
         </is>
       </c>
     </row>
@@ -1519,72 +1519,72 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>160</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>119827</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>108075</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>130571</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>71,18%</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>64,2%</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>77,56%</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
           <t>154</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
-        <is>
-          <t>136366</t>
-        </is>
-      </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>121658</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>158040</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
-        <is>
-          <t>71,62%</t>
-        </is>
-      </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>63,9%</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>83,0%</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>160</t>
-        </is>
-      </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>131698</t>
+          <t>106553</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>118833</t>
+          <t>96491</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>143856</t>
+          <t>116769</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>71,08%</t>
+          <t>67,85%</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>64,13%</t>
+          <t>61,44%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>77,64%</t>
+          <t>74,35%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1594,32 +1594,32 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>268064</t>
+          <t>226380</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>246745</t>
+          <t>211908</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>293833</t>
+          <t>243205</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
         <is>
-          <t>71,35%</t>
+          <t>69,57%</t>
         </is>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>65,68%</t>
+          <t>65,12%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>78,21%</t>
+          <t>74,74%</t>
         </is>
       </c>
     </row>
@@ -1632,57 +1632,57 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>225</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>168341</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>168341</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>168341</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
           <t>227</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
-        <is>
-          <t>190401</t>
-        </is>
-      </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>190401</t>
-        </is>
-      </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>190401</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>225</t>
-        </is>
-      </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>185286</t>
+          <t>157050</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>185286</t>
+          <t>157050</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>185286</t>
+          <t>157050</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1707,17 +1707,17 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>375687</t>
+          <t>325391</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>375687</t>
+          <t>325391</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>375687</t>
+          <t>325391</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1749,72 +1749,72 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>109</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>79895</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>68802</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>91068</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>47,44%</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>40,85%</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>54,07%</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
           <t>115</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
-        <is>
-          <t>83848</t>
-        </is>
-      </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>72905</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>94616</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
-        <is>
-          <t>50,14%</t>
-        </is>
-      </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>43,6%</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>56,58%</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>109</t>
-        </is>
-      </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>84462</t>
+          <t>84485</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>71740</t>
+          <t>73272</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>96235</t>
+          <t>94948</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>46,85%</t>
+          <t>50,76%</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>39,79%</t>
+          <t>44,03%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>53,38%</t>
+          <t>57,05%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1824,32 +1824,32 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>168310</t>
+          <t>164380</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>151240</t>
+          <t>148244</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>185828</t>
+          <t>179650</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
-          <t>48,43%</t>
+          <t>49,09%</t>
         </is>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>43,52%</t>
+          <t>44,27%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>53,47%</t>
+          <t>53,65%</t>
         </is>
       </c>
     </row>
@@ -1862,72 +1862,72 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>128</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>88524</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>77351</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>99617</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>52,56%</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>45,93%</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>59,15%</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
           <t>124</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
-        <is>
-          <t>83379</t>
-        </is>
-      </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>72611</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>94322</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
-        <is>
-          <t>49,86%</t>
-        </is>
-      </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>43,42%</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>56,4%</t>
-        </is>
-      </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>128</t>
-        </is>
-      </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>95833</t>
+          <t>81944</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>84060</t>
+          <t>71481</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>108555</t>
+          <t>93157</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>53,15%</t>
+          <t>49,24%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>46,62%</t>
+          <t>42,95%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>60,21%</t>
+          <t>55,97%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1937,32 +1937,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>179212</t>
+          <t>170468</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>161694</t>
+          <t>155198</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>196282</t>
+          <t>186604</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>51,57%</t>
+          <t>50,91%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>46,53%</t>
+          <t>46,35%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>56,48%</t>
+          <t>55,73%</t>
         </is>
       </c>
     </row>
@@ -1975,57 +1975,57 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
+          <t>237</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>168419</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>168419</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>168419</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
           <t>239</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
-        <is>
-          <t>167227</t>
-        </is>
-      </c>
-      <c r="E15" s="2" t="inlineStr">
-        <is>
-          <t>167227</t>
-        </is>
-      </c>
-      <c r="F15" s="2" t="inlineStr">
-        <is>
-          <t>167227</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>237</t>
-        </is>
-      </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>180295</t>
+          <t>166429</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>180295</t>
+          <t>166429</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>180295</t>
+          <t>166429</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -2050,17 +2050,17 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>347522</t>
+          <t>334848</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>347522</t>
+          <t>334848</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>347522</t>
+          <t>334848</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -2092,72 +2092,72 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>374</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>273735</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>248371</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>297023</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>39,11%</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>35,49%</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>42,44%</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
           <t>373</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
-        <is>
-          <t>259364</t>
-        </is>
-      </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>227582</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>284129</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
-        <is>
-          <t>39,04%</t>
-        </is>
-      </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>34,25%</t>
-        </is>
-      </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>42,76%</t>
-        </is>
-      </c>
-      <c r="J16" s="2" t="inlineStr">
-        <is>
-          <t>374</t>
-        </is>
-      </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>287252</t>
+          <t>259338</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>263853</t>
+          <t>239667</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>314141</t>
+          <t>280734</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>37,75%</t>
+          <t>41,3%</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>34,67%</t>
+          <t>38,17%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>41,28%</t>
+          <t>44,71%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2167,32 +2167,32 @@
       </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
-          <t>546616</t>
+          <t>533073</t>
         </is>
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>503894</t>
+          <t>499121</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>581534</t>
+          <t>564113</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
         <is>
-          <t>38,35%</t>
+          <t>40,15%</t>
         </is>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>35,35%</t>
+          <t>37,59%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>40,8%</t>
+          <t>42,49%</t>
         </is>
       </c>
     </row>
@@ -2205,72 +2205,72 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
+          <t>602</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>426137</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>402849</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>451501</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>60,89%</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>57,56%</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>64,51%</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
           <t>568</t>
         </is>
       </c>
-      <c r="D17" s="2" t="inlineStr">
-        <is>
-          <t>405057</t>
-        </is>
-      </c>
-      <c r="E17" s="2" t="inlineStr">
-        <is>
-          <t>380292</t>
-        </is>
-      </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>436839</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
-        <is>
-          <t>60,96%</t>
-        </is>
-      </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>57,24%</t>
-        </is>
-      </c>
-      <c r="I17" s="2" t="inlineStr">
-        <is>
-          <t>65,75%</t>
-        </is>
-      </c>
-      <c r="J17" s="2" t="inlineStr">
-        <is>
-          <t>602</t>
-        </is>
-      </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>473776</t>
+          <t>368549</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>446887</t>
+          <t>347153</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>497175</t>
+          <t>388220</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>62,25%</t>
+          <t>58,7%</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>58,72%</t>
+          <t>55,29%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>65,33%</t>
+          <t>61,83%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2280,32 +2280,32 @@
       </c>
       <c r="R17" s="2" t="inlineStr">
         <is>
-          <t>878833</t>
+          <t>794686</t>
         </is>
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>843915</t>
+          <t>763646</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>921555</t>
+          <t>828638</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
         <is>
-          <t>61,65%</t>
+          <t>59,85%</t>
         </is>
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>59,2%</t>
+          <t>57,51%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>64,65%</t>
+          <t>62,41%</t>
         </is>
       </c>
     </row>
@@ -2318,57 +2318,57 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
+          <t>976</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>699872</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>699872</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>699872</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
           <t>941</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
-        <is>
-          <t>664421</t>
-        </is>
-      </c>
-      <c r="E18" s="2" t="inlineStr">
-        <is>
-          <t>664421</t>
-        </is>
-      </c>
-      <c r="F18" s="2" t="inlineStr">
-        <is>
-          <t>664421</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J18" s="2" t="inlineStr">
-        <is>
-          <t>976</t>
-        </is>
-      </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>761028</t>
+          <t>627887</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>761028</t>
+          <t>627887</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>761028</t>
+          <t>627887</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2393,17 +2393,17 @@
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t>1425449</t>
+          <t>1327759</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>1425449</t>
+          <t>1327759</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>1425449</t>
+          <t>1327759</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
